--- a/accountant-skill/data/output/Jan2026/audit_validation_Jan2026.xlsx
+++ b/accountant-skill/data/output/Jan2026/audit_validation_Jan2026.xlsx
@@ -104,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -118,11 +118,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -169,6 +197,26 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -541,13 +589,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -573,24 +621,27 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>VALIDATION SUMMARY</t>
         </is>
       </c>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
@@ -603,12 +654,12 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="22" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
@@ -619,12 +670,12 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="23" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr"/>
@@ -635,12 +686,12 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
-        <v>0</v>
+      <c r="B9" s="24" t="n">
+        <v>1</v>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -651,7 +702,7 @@
           <t>SKIP</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="25" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -663,19 +714,23 @@
     </row>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>OVERALL RESULT</t>
         </is>
       </c>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="20" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>All Critical Checks:</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -683,29 +738,33 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>DETAILED RESULTS</t>
         </is>
       </c>
+      <c r="B15" s="19" t="n"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="20" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>Check Name</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>Details</t>
         </is>
@@ -713,11 +772,15 @@
       <c r="E16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>DOUBLE-ENTRY</t>
         </is>
       </c>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="20" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -730,7 +793,7 @@
           <t>Module 4 - All Adjusting Entries</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -743,11 +806,15 @@
       <c r="E18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>CROSS-MODULE FLOW</t>
         </is>
       </c>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="20" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -760,7 +827,7 @@
           <t>Module 3 -&gt; Module 4 (Bank Recon ADJ)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -783,7 +850,7 @@
           <t>Module 4 -&gt; Module 5 (Adj Entries to TB)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -796,11 +863,15 @@
       <c r="E21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>FINANCIAL VALIDATION</t>
         </is>
       </c>
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="20" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -813,7 +884,7 @@
           <t>Balance Sheet: Assets = Equity + Liabilities</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -836,7 +907,7 @@
           <t>Balance Sheet (Dashboard Check)</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -876,13 +947,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -945,7 +1016,7 @@
           <t>Module 4 - All Adjusting Entries</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -984,13 +1055,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1038,7 +1109,7 @@
           <t>Module 3 -&gt; Module 4 (Bank Recon ADJ)</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1055,7 +1126,7 @@
           <t>Module 4 -&gt; Module 5 (Adj Entries to TB)</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1087,13 +1158,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1141,7 +1212,7 @@
           <t>Balance Sheet: Assets = Equity + Liabilities</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1158,7 +1229,7 @@
           <t>Balance Sheet (Dashboard Check)</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1186,17 +1257,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1242,7 +1313,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="9" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -1267,7 +1338,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="9" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -1288,6 +1359,31 @@
       <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Dashboard validation: FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Data Load</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Module 1</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Module 1: books_of_prime_entry*.xlsx not found</t>
         </is>
       </c>
     </row>

--- a/accountant-skill/data/output/Jan2026/audit_validation_Jan2026.xlsx
+++ b/accountant-skill/data/output/Jan2026/audit_validation_Jan2026.xlsx
@@ -11,7 +11,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Double-Entry Checks" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross-Module Flow" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Validation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,10 +63,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00006100"/>
     </font>
   </fonts>
@@ -104,7 +99,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -118,39 +113,11 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -190,33 +157,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -589,13 +533,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -621,27 +565,24 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>VALIDATION SUMMARY</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
@@ -654,12 +595,12 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
-        <v>3</v>
+      <c r="B7" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
@@ -670,12 +611,12 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="B8" s="23" t="n">
-        <v>2</v>
+      <c r="B8" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr"/>
@@ -686,12 +627,12 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
-        <v>1</v>
+      <c r="B9" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -702,7 +643,7 @@
           <t>SKIP</t>
         </is>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="13" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -714,57 +655,49 @@
     </row>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>OVERALL RESULT</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="20" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>All Critical Checks:</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>DETAILED RESULTS</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n"/>
-      <c r="C15" s="19" t="n"/>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="20" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Check Name</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Details</t>
         </is>
@@ -772,15 +705,11 @@
       <c r="E16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>DOUBLE-ENTRY</t>
         </is>
       </c>
-      <c r="B17" s="19" t="n"/>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="19" t="n"/>
-      <c r="E17" s="20" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -793,7 +722,7 @@
           <t>Module 4 - All Adjusting Entries</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -806,15 +735,11 @@
       <c r="E18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>CROSS-MODULE FLOW</t>
         </is>
       </c>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="20" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -827,7 +752,7 @@
           <t>Module 3 -&gt; Module 4 (Bank Recon ADJ)</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -850,28 +775,24 @@
           <t>Module 4 -&gt; Module 5 (Adj Entries to TB)</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Adj accounts=7, TB adj accounts=0</t>
+          <t>Adj accounts=8, TB adj accounts=0</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>FINANCIAL VALIDATION</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="20" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -884,14 +805,14 @@
           <t>Balance Sheet: Assets = Equity + Liabilities</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Assets=12,160,750.00, Equity=9,207,750.00, Liabilities=4,073,000.00, Diff=-1,120,000.00</t>
+          <t>Assets=13,215,750.00, Equity=9,142,750.00, Liabilities=4,073,000.00, Diff=0.00</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr"/>
@@ -907,14 +828,14 @@
           <t>Balance Sheet (Dashboard Check)</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Dashboard validation: FAIL</t>
+          <t>Dashboard validation: PASS</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr"/>
@@ -947,13 +868,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,7 +937,7 @@
           <t>Module 4 - All Adjusting Entries</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1055,13 +976,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1109,7 +1030,7 @@
           <t>Module 3 -&gt; Module 4 (Bank Recon ADJ)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1126,14 +1047,14 @@
           <t>Module 4 -&gt; Module 5 (Adj Entries to TB)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Adj accounts=7, TB adj accounts=0</t>
+          <t>Adj accounts=8, TB adj accounts=0</t>
         </is>
       </c>
     </row>
@@ -1158,13 +1079,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1212,14 +1133,14 @@
           <t>Balance Sheet: Assets = Equity + Liabilities</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Assets=12,160,750.00, Equity=9,207,750.00, Liabilities=4,073,000.00, Diff=-1,120,000.00</t>
+          <t>Assets=13,215,750.00, Equity=9,142,750.00, Liabilities=4,073,000.00, Diff=0.00</t>
         </is>
       </c>
     </row>
@@ -1229,14 +1150,14 @@
           <t>Balance Sheet (Dashboard Check)</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Dashboard validation: FAIL</t>
+          <t>Dashboard validation: PASS</t>
         </is>
       </c>
     </row>
@@ -1248,150 +1169,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00FF0000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Exceptions &amp; Warnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Items requiring attention</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Check Name</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Financial Validation</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Balance Sheet: Assets = Equity + Liabilities</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Assets=12,160,750.00, Equity=9,207,750.00, Liabilities=4,073,000.00, Diff=-1,120,000.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Financial Validation</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Balance Sheet (Dashboard Check)</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Dashboard validation: FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Data Load</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Module 1</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>Module 1: books_of_prime_entry*.xlsx not found</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>